--- a/d/2026-10-03_会员有效性分析.xlsx
+++ b/d/2026-10-03_会员有效性分析.xlsx
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C2" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D2" t="n">
         <v>24</v>
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C7" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1537,19 +1537,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>华为宁德霞浦方圆荟</t>
+          <t>APR北京延庆万达</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E34" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1564,19 +1564,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>华为宁德霞浦方圆荟</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1591,19 +1591,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DJI上海FFC滨江悦里授权体验店</t>
+          <t>APR成都科华王府井</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1618,19 +1618,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DJI北京京西大悦城授权体验店</t>
+          <t>DJI上海FFC滨江悦里授权体验店</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1645,19 +1645,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>APR成都环球中心</t>
+          <t>DJI北京京西大悦城授权体验店</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1672,19 +1672,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DJI上海徐汇万科广场授权体验店</t>
+          <t>APR成都环球中心</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1699,19 +1699,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
+          <t>DJI上海徐汇万科广场授权体验店</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="E40" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1726,19 +1726,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏上海新嘉中心概念店</t>
+          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="E41" t="n">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1753,19 +1753,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>华为福州砂之船奥莱</t>
+          <t>DJI大疆哈苏上海新嘉中心概念店</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E42" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>华为厦门湖里蔡塘爱琴海</t>
+          <t>华为福州砂之船奥莱</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DJI北京西单大悦城授权体验店</t>
+          <t>华为厦门湖里蔡塘爱琴海</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DJI北京石景山万达授权体验店</t>
+          <t>DJI北京西单大悦城授权体验店</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E45" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1861,19 +1861,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>APR北京石景山喜隆多</t>
+          <t>DJI北京石景山万达授权体验店</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E46" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1888,19 +1888,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DJI北京蓝色港湾授权体验店</t>
+          <t>APR北京石景山喜隆多</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E47" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DJI北京顺义华联授权体验店</t>
+          <t>DJI北京蓝色港湾授权体验店</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E48" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -1942,19 +1942,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DJI上海江桥万达授权体验店</t>
+          <t>DJI北京顺义华联授权体验店</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="E49" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1969,19 +1969,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>APR北京东坝万达</t>
+          <t>DJI上海江桥万达授权体验店</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E50" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -1996,19 +1996,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DJI北京龙湖长安天街授权体验店</t>
+          <t>APR北京东坝万达</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2023,19 +2023,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>华为北京丰科万达</t>
+          <t>DJI北京龙湖长安天街授权体验店</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E52" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2050,19 +2050,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>APR成都高新伊藤</t>
+          <t>华为北京丰科万达</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E53" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2077,19 +2077,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DJI上海天荟广场授权体验店</t>
+          <t>APR成都高新伊藤</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E54" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>华为泉州石狮泰禾广场</t>
+          <t>DJI上海天荟广场授权体验店</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E55" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2131,19 +2131,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>华为泉州石狮泰禾广场</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>华为北京石景山万达</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E57" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2185,19 +2185,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>APR成都龙泉吾悦</t>
+          <t>华为北京石景山万达</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E58" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2212,14 +2212,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DJI上海嘉亭荟授权体验店</t>
+          <t>APR成都龙泉吾悦</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E59" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2234,19 +2239,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>华为南平建阳建发悦城</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>福建易联</t>
+          <t>DJI上海嘉亭荟授权体验店</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E60" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2261,19 +2261,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
+          <t>华为南平建阳建发悦城</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="E61" t="n">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -2288,19 +2288,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>APR北京颐堤港</t>
+          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="E62" t="n">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -2315,19 +2315,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>华为北京亦庄龙湖</t>
+          <t>APR北京颐堤港</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -2342,19 +2342,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>APR成都温江旭辉</t>
+          <t>华为北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E64" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -2369,19 +2369,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DJI北京金源购物广场授权体验店</t>
+          <t>APR成都温江旭辉</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E65" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2396,19 +2396,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DJI上海百联又一城授权体验店</t>
+          <t>DJI北京金源购物广场授权体验店</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E66" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>DJI上海百联又一城授权体验店</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E67" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DJI上海维璟印象城授权体验店</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E68" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2477,19 +2477,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>华为北京丽泽龙湖</t>
+          <t>DJI上海维璟印象城授权体验店</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E69" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2504,19 +2504,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>APR北京回龙观华联</t>
+          <t>华为北京丽泽龙湖</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E70" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -2531,19 +2531,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DJI上海虹口凯德授权体验店</t>
+          <t>APR北京回龙观华联</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E71" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海虹口凯德授权体验店</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E72" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -2585,19 +2585,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -2612,12 +2612,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DJI北京龙湖大兴天街授权体验店</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2639,19 +2639,19 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>华为北京东坝万达</t>
+          <t>DJI北京龙湖大兴天街授权体验店</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E75" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -2666,19 +2666,19 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>APR成都蜀新天街</t>
+          <t>华为北京东坝万达</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="E76" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -2693,19 +2693,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>APR北京石景山万达</t>
+          <t>APR成都蜀新天街</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E77" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -2720,19 +2720,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DJI北京朝阳大悦城授权体验店</t>
+          <t>APR北京石景山万达</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E78" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -2747,19 +2747,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>APR成都三利爱琴海</t>
+          <t>DJI北京朝阳大悦城授权体验店</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -2774,19 +2774,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DJI北京太阳宫凯德授权体验店</t>
+          <t>APR成都三利爱琴海</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -2801,19 +2801,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>APR北京西三旗万象汇</t>
+          <t>DJI北京太阳宫凯德授权体验店</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E81" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>APR北京大兴龙湖</t>
+          <t>APR北京西三旗万象汇</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>APR北京大族广场</t>
+          <t>APR北京大兴龙湖</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E83" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -2882,19 +2882,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DJI上海中庚漫游城授权体验店</t>
+          <t>APR北京大族广场</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E84" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -2909,19 +2909,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>DJI上海中庚漫游城授权体验店</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="E85" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -2936,19 +2936,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>APR北京房山龙湖</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2963,19 +2963,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DJI北京长楹天街授权体验店</t>
+          <t>APR北京房山龙湖</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E87" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -2990,19 +2990,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>华为北京房山万科</t>
+          <t>DJI北京长楹天街授权体验店</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3017,19 +3017,19 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DJI北京东坝万达广场授权体验店</t>
+          <t>华为北京房山万科</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E89" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -3044,19 +3044,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>APR成都凯德魅力城</t>
+          <t>DJI北京东坝万达广场授权体验店</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E90" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -3071,19 +3071,19 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>APR北京房山熙悦</t>
+          <t>APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E91" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -3098,19 +3098,19 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>APR北京房山熙悦</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E92" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -3125,19 +3125,19 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>APR成都北城天街</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -3152,19 +3152,19 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DJI北京昌平悦荟授权体验店</t>
+          <t>APR成都北城天街</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E94" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DJI北京通州万达授权体验店</t>
+          <t>DJI北京昌平悦荟授权体验店</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E95" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -3206,19 +3206,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>APR成都新光天地</t>
+          <t>DJI北京通州万达授权体验店</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E96" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3233,19 +3233,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>APR北京延庆万达</t>
+          <t>APR成都新光天地</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E97" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -9239,12 +9239,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+256GB) 曜石黑</t>
+          <t>Mate 90 Pro Max CMM-AL10(16GB+512GB) 曜石黑</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6942711326045</t>
+          <t>6942711326519</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mate 90 Pro Max CMM-AL10(16GB+512GB) 曜石黑</t>
+          <t>Mate 90 HLS-AL00(12GB+256GB) 曜石黑</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6942711326519</t>
+          <t>6942711326045</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Mate 90 Pro Max CMM-AL10(16GB+512GB) 曜石黑</t>
+          <t>Mate 90 HLS-AL00(12GB+256GB) 曜石黑</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6942711326519</t>
+          <t>6942711326045</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+256GB) 曜石黑</t>
+          <t>Mate 90 HLS-AL00(12GB+256GB) 晶格粉</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6942711326045</t>
+          <t>6942711326076</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -10059,17 +10059,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Watch系列</t>
+          <t>Mate 90</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>WATCH 6 Pro NIZ-AL00 46mm(深锖色钛金属表带)太空探索</t>
+          <t>Mate 90 HLS-AL00(12GB+256GB) 曜石黑</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6942711313847</t>
+          <t>6942711326045</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -10114,17 +10114,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Mate 90</t>
+          <t>Watch系列</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+256GB) 曜石黑</t>
+          <t>WATCH 6 Pro NIZ-AL00 46mm(深锖色钛金属表带)太空探索</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6942711326045</t>
+          <t>6942711313847</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+256GB) 晶格粉</t>
+          <t>Mate 90 Pro Max CMM-AL10(16GB+512GB) 曜石黑</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6942711326076</t>
+          <t>6942711326519</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 曜石黑</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 翡冷翠</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>6942711325628</t>
+          <t>6942711325642</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 曜石黑</t>
+          <t>Mate 90 HLS-AL00(12GB+512GB) 曜石黑</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6942711325628</t>
+          <t>6942711326083</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -10559,12 +10559,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+512GB) 曜石黑</t>
+          <t>Mate 90 HLS-AL00(12GB+512GB) 零度白</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>6942711326083</t>
+          <t>6942711326090</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 翡冷翠</t>
+          <t>Mate 90 HLS-AL00(12GB+512GB) 晶格绿</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>6942711325642</t>
+          <t>6942711326106</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+512GB) 晶格绿</t>
+          <t>Mate 90 HLS-AL00(12GB+512GB) 曜石黑</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>6942711326106</t>
+          <t>6942711326083</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -10724,12 +10724,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
+          <t>Mate 90 Pro Max CMM-AL10(16GB+512GB) 曜石黑</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6942711325635</t>
+          <t>6942711326519</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+512GB) 曜石黑</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 曜石黑</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6942711326083</t>
+          <t>6942711325628</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mate 90 Pro Max CMM-AL10(16GB+512GB) 曜石黑</t>
+          <t>Mate 90 HLS-AL00(12GB+512GB) 曜石黑</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>6942711326519</t>
+          <t>6942711326083</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 翡冷翠</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 曜石黑</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>6942711325642</t>
+          <t>6942711325628</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -10999,12 +10999,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 翡冷翠</t>
+          <t>Mate 90 HLS-AL00(12GB+512GB) 零度白</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>6942711325642</t>
+          <t>6942711326090</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -11054,12 +11054,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+512GB) 零度白</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 翡冷翠</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6942711326090</t>
+          <t>6942711325642</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -11109,12 +11109,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+512GB) 零度白</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>6942711326090</t>
+          <t>6942711325635</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+512GB) 曜石黑</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 翡冷翠</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6942711326083</t>
+          <t>6942711325642</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+512GB) 零度白</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 翡冷翠</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6942711326090</t>
+          <t>6942711325642</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 翡冷翠</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>6942711325635</t>
+          <t>6942711325642</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 曜石黑</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>6942711325628</t>
+          <t>6942711325635</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -11549,12 +11549,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+256GB) 零度白</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>6942711326052</t>
+          <t>6942711325635</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 曜石黑</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>6942711325635</t>
+          <t>6942711325628</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -11659,12 +11659,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 曜石黑</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>6942711325635</t>
+          <t>6942711325628</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -11714,12 +11714,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 曜石黑</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>6942711325628</t>
+          <t>6942711325635</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
+          <t>Mate 90 HLS-AL00(12GB+512GB) 零度白</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>6942711325635</t>
+          <t>6942711326090</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+512GB) 零度白</t>
+          <t>Mate 90 HLS-AL00(12GB+256GB) 零度白</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>6942711326090</t>
+          <t>6942711326052</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+256GB) 零度白</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>6942711326052</t>
+          <t>6942711325635</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -12044,12 +12044,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+256GB) 曜石黑</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 翡冷翠</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>6942711326045</t>
+          <t>6942711325642</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -12099,12 +12099,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 曜石黑</t>
+          <t>Mate 90 HLS-AL00(12GB+256GB) 曜石黑</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>6942711325628</t>
+          <t>6942711326045</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -12154,12 +12154,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 曜石黑</t>
+          <t>Mate 90 HLS-AL00(12GB+512GB) 零度白</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>6942711325628</t>
+          <t>6942711326090</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 翡冷翠</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 曜石黑</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>6942711325642</t>
+          <t>6942711325628</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 翡冷翠</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 曜石黑</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>6942711325642</t>
+          <t>6942711325628</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -12374,12 +12374,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 翡冷翠</t>
+          <t>Mate 90 HLS-AL00(12GB+256GB) 零度白</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>6942711325642</t>
+          <t>6942711326052</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -13129,17 +13129,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
+          <t>COOYEE可怡 iphone  18 Pro Max御甲肤感磁吸壳 浅蓝色</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>6955482543900</t>
+          <t>6971070086253</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -13200,17 +13200,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>6927123816285</t>
+          <t>6955482543900</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -13276,12 +13276,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
+          <t>ZGA iPhone 18 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>6927123816537</t>
+          <t>6927123816285</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -13347,12 +13347,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>COOYEE可怡 iphone  18 Pro Max御甲肤感磁吸壳 浅蓝色</t>
+          <t>ZGA iPhone 18 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>6971070086253</t>
+          <t>6927123816285</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -13418,12 +13418,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6927123816285</t>
+          <t>6927123816537</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -13484,17 +13484,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max 256GB 勃艮第酒红色 - MJY84CH/A</t>
+          <t>AppleCare Services for iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>195****11804</t>
+          <t>195****94450</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -13555,17 +13555,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 18 Pro Max</t>
+          <t>iPhone 18 Pro Max 256GB 勃艮第酒红色 - MJY84CH/A</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>195****94450</t>
+          <t>195****11804</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -13631,12 +13631,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
+          <t>ZGA iPhone 18 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6927123816537</t>
+          <t>6927123816308</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
+          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6927123816308</t>
+          <t>6927123816537</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -13986,12 +13986,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
+          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>6927123816308</t>
+          <t>6927123816537</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -14057,12 +14057,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -14123,17 +14123,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>VOKAMO沃咔曼 iPhone 18 Pro Max 液态硅胶磁吸保护壳 云絮白</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>6980113280114</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -14194,17 +14194,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 18 Pro Max 液态硅胶磁吸保护壳 云絮白</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6980113280114</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -14270,12 +14270,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
+          <t>ZGA iPhone 18 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6927123816537</t>
+          <t>6927123816308</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -14407,17 +14407,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 远峰蓝</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6927123816285</t>
+          <t>6955482537602</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -14478,17 +14478,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>音乐</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>AirPods 5 (配无线充电盒) - MKFT4CH/A</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>195****78596</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -14549,17 +14549,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>音乐</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>AirPods 5 (配无线充电盒) - MKFT4CH/A</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>195****78596</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -14620,17 +14620,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 远峰蓝</t>
+          <t>ZGA iPhone 18 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>6955482537602</t>
+          <t>6927123816285</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -14767,12 +14767,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>6927123810405</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -14980,12 +14980,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6927123810405</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -15756,17 +15756,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>COOYEE可怡 iphone  18 Pro Max御甲肤感磁吸壳 浅蓝色</t>
+          <t>MAXCO美能格 MP26 未来磁吸双向快充移动电源</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>6971070086253</t>
+          <t>6955482530214</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -15903,12 +15903,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MP26 未来磁吸双向快充移动电源</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>6955482530214</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -15969,17 +15969,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>VOKAMO沃咔曼 iPhone 18 Pro / 18 Pro Max冰晶 AR 增透镜头保护膜 透明</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>6980113280282</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -16040,17 +16040,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 18 Pro / 18 Pro Max冰晶 AR 增透镜头保护膜 透明</t>
+          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>6980113280282</t>
+          <t>6955482543900</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -16111,17 +16111,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
+          <t>COOYEE可怡 iphone  18 Pro Max御甲肤感磁吸壳 浅蓝色</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>6955482543900</t>
+          <t>6971070086253</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -16253,17 +16253,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
+          <t>VOKAMO沃咔曼 iPhone 18 Pro 轻薄肤感磁吸保护壳 霜雪白</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>6955482543900</t>
+          <t>6980113280343</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -16324,17 +16324,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 18 Pro 轻薄肤感磁吸保护壳 霜雪白</t>
+          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>6980113280343</t>
+          <t>6955482543900</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -16542,12 +16542,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 18 Pro Max 钻石高清三强钢化玻璃膜 黑</t>
+          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>6980113280237</t>
+          <t>6927123816537</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -16608,17 +16608,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 18 Pro Max 钻石高清三强钢化玻璃膜 黑</t>
+          <t>MAXCO美能格 MP26 未来磁吸双向快充移动电源</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>6980113280237</t>
+          <t>6955482530214</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -16679,17 +16679,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MP26 未来磁吸双向快充移动电源</t>
+          <t>VOKAMO沃咔曼 iPhone 18 Pro Max 钻石高清三强钢化玻璃膜 黑</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>6955482530214</t>
+          <t>6980113280237</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -16750,17 +16750,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
+          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>6927123816537</t>
+          <t>6955482543900</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -16821,17 +16821,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
+          <t>VOKAMO沃咔曼 iPhone 18 Pro Max 钻石高清三强钢化玻璃膜 黑</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>6955482543900</t>
+          <t>6980113280237</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro Max 流彩液态 360 度旋转支架保护壳 黑色</t>
+          <t>ZGA iPhone 18 Pro Max 飞舞 360 度旋转支架保护壳 白色</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>6927123817015</t>
+          <t>6927123816964</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -17039,12 +17039,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro Max 飞舞 360 度旋转支架保护壳 白色</t>
+          <t>ZGA iPhone 18 Pro Max 流彩液态 360 度旋转支架保护壳 黑色</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>6927123816964</t>
+          <t>6927123817015</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -17602,17 +17602,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>ZGA iPhone 18 Pro Max 飞舞 360 度旋转支架保护壳 黑色</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>6927123816933</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -17886,17 +17886,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro Max 飞舞 360 度旋转支架保护壳 黑色</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>6927123816933</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -18525,17 +18525,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 晶钻玻璃磁吸保护壳 闪粉银 iPhone 17</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>6927123811235</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -18601,12 +18601,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 晶钻玻璃磁吸保护壳 闪粉银 iPhone 17</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6927123811235</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -18667,17 +18667,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -19453,12 +19453,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro 512GB 冰川蓝色 - MJTF4CH/A</t>
+          <t>iPhone 18 Pro 512GB 银色 - MJTD4CH/A</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>195****17493</t>
+          <t>195****17479</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro 512GB 银色 - MJTD4CH/A</t>
+          <t>iPhone 18 Pro 512GB 冰川蓝色 - MJTF4CH/A</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>195****17479</t>
+          <t>195****17493</t>
         </is>
       </c>
       <c r="L92" t="n">
@@ -20158,20 +20158,23 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro 防偷窥防静电二强钢化膜 黑色</t>
+          <t>CLEER可丽尔 ARC 6 开放式 AI 耳机 曜石黑</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>6927123810351</t>
+          <t>6938741702942</t>
         </is>
       </c>
       <c r="L101" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" t="n">
         <v>1</v>
       </c>
       <c r="N101" t="n">
@@ -20226,23 +20229,20 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>CLEER可丽尔 ARC 6 开放式 AI 耳机 曜石黑</t>
+          <t>ZGA iPhone 17 Pro 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>6938741702942</t>
+          <t>6927123810351</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1</v>
-      </c>
-      <c r="M102" t="n">
         <v>1</v>
       </c>
       <c r="N102" t="n">
@@ -28373,17 +28373,17 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Nano</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（中号）</t>
+          <t>DJI Care 随心换 1年版（Osmo Nano）中国版</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>6937224129511</t>
+          <t>6937224116146</t>
         </is>
       </c>
       <c r="L217" t="n">
@@ -28449,12 +28449,12 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo Nano）中国版</t>
+          <t>Osmo Nano (128GB)</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>6937224116146</t>
+          <t>6937224115453</t>
         </is>
       </c>
       <c r="L218" t="n">
@@ -28515,17 +28515,17 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Nano</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Osmo Nano (128GB)</t>
+          <t>DJI 无纺布购物袋（中号）</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>6937224115453</t>
+          <t>6937224129511</t>
         </is>
       </c>
       <c r="L219" t="n">
@@ -32248,17 +32248,17 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>保护膜</t>
+          <t>雷克沙</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>X.ONE 大疆 Osmo Action 6 AR 增透保护膜</t>
+          <t>雷克沙 Silver 极速TF存储卡Micro SD卡  256G</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>6937634521646</t>
+          <t>843367135394</t>
         </is>
       </c>
       <c r="L272" t="n">
@@ -32324,15 +32324,18 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Osmo 挂脖支架 Max</t>
+          <t>Osmo 耐寒增强续航电池（2150 mAh）</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>6941565998507</t>
+          <t>6937224148833</t>
         </is>
       </c>
       <c r="L273" t="n">
+        <v>1</v>
+      </c>
+      <c r="M273" t="n">
         <v>1</v>
       </c>
       <c r="N273" t="n">
@@ -32455,23 +32458,20 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Osmo 耐寒增强续航电池（2150 mAh）</t>
+          <t>DJI 无纺布购物袋（中号）</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>6937224148833</t>
+          <t>6937224129511</t>
         </is>
       </c>
       <c r="L275" t="n">
-        <v>1</v>
-      </c>
-      <c r="M275" t="n">
         <v>1</v>
       </c>
       <c r="N275" t="n">
@@ -32526,17 +32526,17 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（中号）</t>
+          <t>DJI Care 随心换 1年版（Osmo Action 6）中国版</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>6937224129511</t>
+          <t>6937224124783</t>
         </is>
       </c>
       <c r="L276" t="n">
@@ -32594,20 +32594,23 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>保护膜</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo Action 6）中国版</t>
+          <t>X.ONE 大疆 Osmo Action 6 AR 增透保护膜</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>6937224124783</t>
+          <t>6937634521646</t>
         </is>
       </c>
       <c r="L277" t="n">
+        <v>1</v>
+      </c>
+      <c r="M277" t="n">
         <v>1</v>
       </c>
       <c r="N277" t="n">
@@ -32662,23 +32665,20 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>雷克沙</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>雷克沙 Silver 极速TF存储卡Micro SD卡  256G</t>
+          <t>Osmo 挂脖支架 Max</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>843367135394</t>
+          <t>6941565998507</t>
         </is>
       </c>
       <c r="L278" t="n">
-        <v>1</v>
-      </c>
-      <c r="M278" t="n">
         <v>1</v>
       </c>
       <c r="N278" t="n">
@@ -34422,17 +34422,17 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>nova 15</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>礼品-定制-沙发嘿嘿摆件1</t>
+          <t>nova 15 PSN-AL00（12GB+256GB）零度白</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>A0800812</t>
+          <t>6942103181566</t>
         </is>
       </c>
       <c r="L303" t="n">
@@ -34493,17 +34493,17 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>nova 15</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>nova 15 PSN-AL00（12GB+256GB）零度白</t>
+          <t>礼品-定制-沙发嘿嘿摆件1</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>6942103181566</t>
+          <t>A0800812</t>
         </is>
       </c>
       <c r="L304" t="n">
@@ -34777,17 +34777,17 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>MateBook Pro S</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>MateBook Pro S MOR-M1(HarmonyOS 24GB+512GB)触屏 烟云灰</t>
+          <t>礼品-配件-无线鼠标-CD23 SE-黑色-55036863</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>6942711312994</t>
+          <t>A0890186</t>
         </is>
       </c>
       <c r="L308" t="n">
@@ -34848,17 +34848,17 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>MateBook Pro S</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>礼品-配件-无线鼠标-CD23 SE-黑色-55036863</t>
+          <t>MateBook Pro S MOR-M1(HarmonyOS 24GB+512GB)触屏 烟云灰</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>A0890186</t>
+          <t>6942711312994</t>
         </is>
       </c>
       <c r="L309" t="n">
@@ -35484,20 +35484,23 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>Mate 90</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>礼品-通用-随行杯-香槟金</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>A0800801</t>
+          <t>6942711325635</t>
         </is>
       </c>
       <c r="L318" t="n">
+        <v>1</v>
+      </c>
+      <c r="M318" t="n">
         <v>1</v>
       </c>
       <c r="N318" t="n">
@@ -35552,23 +35555,20 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>Mate 90</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
+          <t>礼品-通用-随行杯-香槟金</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>6942711325635</t>
+          <t>A0800801</t>
         </is>
       </c>
       <c r="L319" t="n">
-        <v>1</v>
-      </c>
-      <c r="M319" t="n">
         <v>1</v>
       </c>
       <c r="N319" t="n">
@@ -36046,20 +36046,23 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>MatePad Pro Max</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>礼品-配件-HUAWEI MatePad 13.2吋（GellMann）智能皮套-51996248-砚黑</t>
+          <t>MatePad Pro Max WIFI 12GB+512GB 柔光版 曜石灰</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>A0891150</t>
+          <t>6942103197888</t>
         </is>
       </c>
       <c r="L326" t="n">
+        <v>1</v>
+      </c>
+      <c r="M326" t="n">
         <v>1</v>
       </c>
       <c r="N326" t="n">
@@ -36114,23 +36117,20 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>MatePad Pro Max</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>MatePad Pro Max WIFI 12GB+512GB 柔光版 曜石灰</t>
+          <t>礼品-配件-HUAWEI MatePad 13.2吋（GellMann）智能皮套-51996248-砚黑</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>6942103197888</t>
+          <t>A0891150</t>
         </is>
       </c>
       <c r="L327" t="n">
-        <v>1</v>
-      </c>
-      <c r="M327" t="n">
         <v>1</v>
       </c>
       <c r="N327" t="n">
@@ -37741,17 +37741,17 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>Mate 90</t>
+          <t>权益礼包</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>Mate 90 Pro Max 典藏版 CMM-AL10(16GB+1TB) 曜石黑</t>
+          <t>499元套包</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>6942711326632</t>
+          <t>BJYLVIP0004</t>
         </is>
       </c>
       <c r="L350" t="n">
@@ -37812,17 +37812,17 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>权益礼包</t>
+          <t>Mate 90</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>499元套包</t>
+          <t>Mate 90 Pro Max 典藏版 CMM-AL10(16GB+1TB) 曜石黑</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>BJYLVIP0004</t>
+          <t>6942711326632</t>
         </is>
       </c>
       <c r="L351" t="n">
@@ -38096,20 +38096,23 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>Mate 80</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>礼品-定制-圆脸憨憨1</t>
+          <t>Mate 80 VYG-AL30(16GB+512GB) 雪域白</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>A0800806</t>
+          <t>6942103191671</t>
         </is>
       </c>
       <c r="L355" t="n">
+        <v>1</v>
+      </c>
+      <c r="M355" t="n">
         <v>1</v>
       </c>
       <c r="N355" t="n">
@@ -38164,23 +38167,20 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>Mate 80</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>Mate 80 VYG-AL30(16GB+512GB) 雪域白</t>
+          <t>礼品-定制-圆脸憨憨1</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>6942103191671</t>
+          <t>A0800806</t>
         </is>
       </c>
       <c r="L356" t="n">
-        <v>1</v>
-      </c>
-      <c r="M356" t="n">
         <v>1</v>
       </c>
       <c r="N356" t="n">
@@ -38448,17 +38448,17 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>华为电源</t>
+          <t>Pura 90</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>华为自带线全能充移动电源（66W 12000） 雪域白</t>
+          <t>Pura 90 Pro MLN-AL00 12GB+512GB 桑果黑</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>6942103180446</t>
+          <t>6942103194115</t>
         </is>
       </c>
       <c r="L360" t="n">
@@ -38519,17 +38519,17 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>Pura 90</t>
+          <t>华为电源</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>Pura 90 Pro MLN-AL00 12GB+512GB 桑果黑</t>
+          <t>华为自带线全能充移动电源（66W 12000） 雪域白</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>6942103194115</t>
+          <t>6942103180446</t>
         </is>
       </c>
       <c r="L361" t="n">
@@ -39589,12 +39589,12 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>6927123816285</t>
+          <t>6927123816537</t>
         </is>
       </c>
       <c r="L376" t="n">
@@ -39797,17 +39797,17 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
+          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>6927123816537</t>
+          <t>6955482543900</t>
         </is>
       </c>
       <c r="L379" t="n">
@@ -39868,17 +39868,17 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
+          <t>VOKAMO沃咔曼 iPhone 18 Pro Max 液态硅胶磁吸保护壳 樱桃红</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>6955482543900</t>
+          <t>6980113280138</t>
         </is>
       </c>
       <c r="L380" t="n">
@@ -39939,17 +39939,17 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 18 Pro Max 液态硅胶磁吸保护壳 樱桃红</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>6980113280138</t>
+          <t>6955482542736</t>
         </is>
       </c>
       <c r="L381" t="n">
@@ -40010,17 +40010,17 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
+          <t>ZGA iPhone 18 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>6955482542736</t>
+          <t>6927123816285</t>
         </is>
       </c>
       <c r="L382" t="n">
@@ -40853,17 +40853,17 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6927123816537</t>
         </is>
       </c>
       <c r="L394" t="n">
@@ -40924,17 +40924,17 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
+          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>6927123816537</t>
+          <t>6955482543900</t>
         </is>
       </c>
       <c r="L395" t="n">
@@ -41000,12 +41000,12 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>6955482543900</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L396" t="n">
@@ -41213,12 +41213,12 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max 512GB 银色 - MJYC4CH/A</t>
+          <t>iPhone 18 Pro Max 256GB 冰川蓝色 - MJY94CH/A</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>195****11835</t>
+          <t>195****11811</t>
         </is>
       </c>
       <c r="L399" t="n">
@@ -41284,12 +41284,12 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max 256GB 冰川蓝色 - MJY94CH/A</t>
+          <t>iPhone 18 Pro Max 512GB 银色 - MJYC4CH/A</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>195****11811</t>
+          <t>195****11835</t>
         </is>
       </c>
       <c r="L400" t="n">
@@ -41421,17 +41421,17 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>6922329935921</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L402" t="n">
@@ -41497,12 +41497,12 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6922329935921</t>
         </is>
       </c>
       <c r="L403" t="n">
@@ -41568,12 +41568,12 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>6927123810436</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L404" t="n">
@@ -41634,17 +41634,17 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6927123810436</t>
         </is>
       </c>
       <c r="L405" t="n">
@@ -41847,17 +41847,17 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
+          <t>VOKAMO沃咔曼 iPhone 18 Pro Max 钻石高清三强钢化玻璃膜 黑</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>6955482543900</t>
+          <t>6980113280237</t>
         </is>
       </c>
       <c r="L408" t="n">
@@ -41989,17 +41989,17 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 18 Pro Max 钻石高清三强钢化玻璃膜 黑</t>
+          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>6980113280237</t>
+          <t>6955482543900</t>
         </is>
       </c>
       <c r="L410" t="n">
@@ -42344,17 +42344,17 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max 256GB 勃艮第酒红色 - MJY84CH/A</t>
+          <t>COOYEE可怡 iphone  18 Pro  Max波浪纹磁吸壳 樱桃红</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>195****11804</t>
+          <t>6971070081029</t>
         </is>
       </c>
       <c r="L415" t="n">
@@ -42486,17 +42486,17 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>COOYEE可怡 iphone  18 Pro  Max波浪纹磁吸壳 樱桃红</t>
+          <t>iPhone 18 Pro Max 256GB 勃艮第酒红色 - MJY84CH/A</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>6971070081029</t>
+          <t>195****11804</t>
         </is>
       </c>
       <c r="L417" t="n">
@@ -42628,23 +42628,20 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 18 Pro Max 钻石高清三强钢化玻璃膜 黑</t>
+          <t>iPhone 18 Pro Max 256GB 勃艮第酒红色 - MJY84CH/A</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>6980113280237</t>
+          <t>195****11804</t>
         </is>
       </c>
       <c r="L419" t="n">
-        <v>1</v>
-      </c>
-      <c r="M419" t="n">
         <v>1</v>
       </c>
       <c r="N419" t="n">
@@ -42704,12 +42701,12 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 18 Pro / 18 Pro Max冰晶 AR 增透镜头保护膜 透明</t>
+          <t>VOKAMO沃咔曼 iPhone 18 Pro Max轻薄肤感磁吸保护壳 樱桃红</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>6980113280282</t>
+          <t>6980113280404</t>
         </is>
       </c>
       <c r="L420" t="n">
@@ -42775,12 +42772,12 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
+          <t>COMMA珂玛 捷豹系列 10000mAh 四合一带线快充移动电源</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>6955482543900</t>
+          <t>6942297112827</t>
         </is>
       </c>
       <c r="L421" t="n">
@@ -42841,17 +42838,17 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>COMMA珂玛 捷豹系列 10000mAh 四合一带线快充移动电源</t>
+          <t>VOKAMO沃咔曼 iPhone 18 Pro / 18 Pro Max冰晶 AR 增透镜头保护膜 透明</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>6942297112827</t>
+          <t>6980113280282</t>
         </is>
       </c>
       <c r="L422" t="n">
@@ -42912,17 +42909,17 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 18 Pro Max轻薄肤感磁吸保护壳 樱桃红</t>
+          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>6980113280404</t>
+          <t>6955482543900</t>
         </is>
       </c>
       <c r="L423" t="n">
@@ -42983,20 +42980,23 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max 256GB 勃艮第酒红色 - MJY84CH/A</t>
+          <t>VOKAMO沃咔曼 iPhone 18 Pro Max 钻石高清三强钢化玻璃膜 黑</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>195****11804</t>
+          <t>6980113280237</t>
         </is>
       </c>
       <c r="L424" t="n">
+        <v>1</v>
+      </c>
+      <c r="M424" t="n">
         <v>1</v>
       </c>
       <c r="N424" t="n">
@@ -43335,17 +43335,17 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>AppleCare Services for iPhone 18 Pro</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>195****94443</t>
         </is>
       </c>
       <c r="L429" t="n">
@@ -43406,17 +43406,17 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
+          <t>ZGA iPhone 18 Pro飞舞 360 度旋转支架保护壳 白色</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>6955482543900</t>
+          <t>6927123816926</t>
         </is>
       </c>
       <c r="L430" t="n">
@@ -43477,17 +43477,17 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>6927123816537</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L431" t="n">
@@ -43619,17 +43619,17 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 18 Pro</t>
+          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>195****94443</t>
+          <t>6955482543900</t>
         </is>
       </c>
       <c r="L433" t="n">
@@ -43695,12 +43695,12 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro飞舞 360 度旋转支架保护壳 白色</t>
+          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>6927123816926</t>
+          <t>6927123816537</t>
         </is>
       </c>
       <c r="L434" t="n">
@@ -45891,17 +45891,17 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>ANKER安克 45W 氮化镓单口充电器 白色</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6978252854549</t>
         </is>
       </c>
       <c r="L465" t="n">
@@ -45962,17 +45962,17 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>ANKER安克 45W 氮化镓单口充电器 白色</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>6978252854549</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L466" t="n">
@@ -46175,17 +46175,17 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 18 Pro Max</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 活力橙</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>195****94450</t>
+          <t>6955482540237</t>
         </is>
       </c>
       <c r="L469" t="n">
@@ -46317,17 +46317,17 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 活力橙</t>
+          <t>AppleCare Services for iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>6955482540237</t>
+          <t>195****94450</t>
         </is>
       </c>
       <c r="L471" t="n">
@@ -50340,24 +50340,24 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>Osmo Action 5 Pro 标准套装</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6941565981066</t>
         </is>
       </c>
       <c r="L528" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M528" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N528" t="n">
         <v>2317</v>
@@ -50553,24 +50553,24 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>Osmo Action 5 Pro 标准套装</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K531" t="inlineStr">
         <is>
-          <t>6941565981066</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L531" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M531" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N531" t="n">
         <v>2317</v>
@@ -54860,17 +54860,17 @@
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>MateBook Fold</t>
         </is>
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>礼品-配件-无线鼠标-CD23 SE-黑色-55036863</t>
+          <t>MateBook Fold | ULTIMATE DESIGN SLM-W24(HarmonyOS 24GB+1TB)触屏 幻影黑</t>
         </is>
       </c>
       <c r="K592" t="inlineStr">
         <is>
-          <t>A0890186</t>
+          <t>6942711312871</t>
         </is>
       </c>
       <c r="L592" t="n">
@@ -54931,17 +54931,17 @@
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>MateBook Fold</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>MateBook Fold | ULTIMATE DESIGN SLM-W24(HarmonyOS 24GB+1TB)触屏 幻影黑</t>
+          <t>礼品-配件-无线鼠标-CD23 SE-黑色-55036863</t>
         </is>
       </c>
       <c r="K593" t="inlineStr">
         <is>
-          <t>6942711312871</t>
+          <t>A0890186</t>
         </is>
       </c>
       <c r="L593" t="n">
@@ -55996,17 +55996,17 @@
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>Mate 90</t>
         </is>
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>礼品-定制-圆脸憨憨4</t>
+          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
         </is>
       </c>
       <c r="K608" t="inlineStr">
         <is>
-          <t>A0800809</t>
+          <t>6942711325635</t>
         </is>
       </c>
       <c r="L608" t="n">
@@ -56067,17 +56067,17 @@
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>Mate 90</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>Mate 90 Pro CMS-AL20(12GB+512GB) 晶钻白</t>
+          <t>礼品-定制-圆脸憨憨4</t>
         </is>
       </c>
       <c r="K609" t="inlineStr">
         <is>
-          <t>6942711325635</t>
+          <t>A0800809</t>
         </is>
       </c>
       <c r="L609" t="n">
@@ -56703,17 +56703,17 @@
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>外设</t>
+          <t>保护</t>
         </is>
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>思腾 DEVIA 星动系列移动电源五代(10000mAh) 黑色</t>
+          <t>思腾 DEVIA Mate 80/80 Pro天启系列高清全屏钢化膜</t>
         </is>
       </c>
       <c r="K618" t="inlineStr">
         <is>
-          <t>6942297104723</t>
+          <t>6942297145122</t>
         </is>
       </c>
       <c r="L618" t="n">
@@ -56774,17 +56774,17 @@
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>保护</t>
+          <t>外设</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>思腾 DEVIA Mate 80 Pro Max乐视界镜头保护膜-黑色</t>
+          <t>思腾 DEVIA 星动系列移动电源五代(10000mAh) 黑色</t>
         </is>
       </c>
       <c r="K619" t="inlineStr">
         <is>
-          <t>6942297141940</t>
+          <t>6942297104723</t>
         </is>
       </c>
       <c r="L619" t="n">
@@ -56850,12 +56850,12 @@
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>思腾 DEVIA Mate 80/80 Pro天启系列高清全屏钢化膜</t>
+          <t>思腾 DEVIA Mate 80 Pro Max乐视界镜头保护膜-黑色</t>
         </is>
       </c>
       <c r="K620" t="inlineStr">
         <is>
-          <t>6942297145122</t>
+          <t>6942297141940</t>
         </is>
       </c>
       <c r="L620" t="n">
@@ -56921,12 +56921,12 @@
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t>6955482542736</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L621" t="n">
@@ -56987,17 +56987,17 @@
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K622" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L622" t="n">
@@ -57058,17 +57058,17 @@
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
+          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
         </is>
       </c>
       <c r="K623" t="inlineStr">
         <is>
-          <t>195****10144</t>
+          <t>6955482543900</t>
         </is>
       </c>
       <c r="L623" t="n">
@@ -57134,12 +57134,12 @@
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>ZGA iPhone 系列 明透磁吸保护壳 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6927123809904</t>
         </is>
       </c>
       <c r="L624" t="n">
@@ -57200,17 +57200,17 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>6955482543900</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L625" t="n">
@@ -57342,17 +57342,17 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6955482542736</t>
         </is>
       </c>
       <c r="L627" t="n">
@@ -57413,17 +57413,17 @@
       </c>
       <c r="I628" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 明透磁吸保护壳 透明 iPhone 17</t>
+          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
         </is>
       </c>
       <c r="K628" t="inlineStr">
         <is>
-          <t>6927123809904</t>
+          <t>195****10144</t>
         </is>
       </c>
       <c r="L628" t="n">
@@ -57910,17 +57910,17 @@
       </c>
       <c r="I635" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>ZGA iPhone 18 Pro Max 飞舞 360 度旋转支架保护壳 酒红色</t>
         </is>
       </c>
       <c r="K635" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>6927123816957</t>
         </is>
       </c>
       <c r="L635" t="n">
@@ -57981,17 +57981,17 @@
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K636" t="inlineStr">
         <is>
-          <t>6927123816285</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L636" t="n">
@@ -58052,17 +58052,17 @@
       </c>
       <c r="I637" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
         </is>
       </c>
       <c r="K637" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6927123816537</t>
         </is>
       </c>
       <c r="L637" t="n">
@@ -58123,17 +58123,17 @@
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro Max 飞舞 360 度旋转支架保护壳 酒红色</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
         <is>
-          <t>6927123816957</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L638" t="n">
@@ -58194,17 +58194,17 @@
       </c>
       <c r="I639" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max 256GB 勃艮第酒红色 - MJY84CH/A</t>
+          <t>AppleCare Services for iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="K639" t="inlineStr">
         <is>
-          <t>195****11804</t>
+          <t>195****94450</t>
         </is>
       </c>
       <c r="L639" t="n">
@@ -58265,17 +58265,17 @@
       </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 18 Pro Max</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t>195****94450</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L640" t="n">
@@ -58341,12 +58341,12 @@
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
+          <t>ZGA iPhone 18 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t>6927123816537</t>
+          <t>6927123816285</t>
         </is>
       </c>
       <c r="L641" t="n">
@@ -58407,17 +58407,17 @@
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>iPhone 18 Pro Max 256GB 勃艮第酒红色 - MJY84CH/A</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>195****11804</t>
         </is>
       </c>
       <c r="L642" t="n">
@@ -58549,17 +58549,17 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 18 Pro Max</t>
+          <t>iPhone 18 Pro Max 512GB 冰川蓝色 - MJYE4CH/A</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>195****94450</t>
+          <t>195****11859</t>
         </is>
       </c>
       <c r="L644" t="n">
@@ -58620,17 +58620,17 @@
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max 512GB 冰川蓝色 - MJYE4CH/A</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
         <is>
-          <t>195****11859</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L645" t="n">
@@ -58762,17 +58762,17 @@
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>ZGA iPhone 18 Pro Max 飞舞 360 度旋转支架保护壳 白色</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>6927123816964</t>
         </is>
       </c>
       <c r="L647" t="n">
@@ -58904,17 +58904,17 @@
       </c>
       <c r="I649" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro Max 飞舞 360 度旋转支架保护壳 白色</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K649" t="inlineStr">
         <is>
-          <t>6927123816964</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L649" t="n">
@@ -58975,17 +58975,17 @@
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>COOYEE可怡 iphone  18 Pro  Max波浪纹磁吸壳 白色</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6971070081104</t>
         </is>
       </c>
       <c r="L650" t="n">
@@ -59046,17 +59046,17 @@
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>COOYEE可怡 iphone  18 Pro  Max波浪纹磁吸壳 白色</t>
+          <t>AppleCare Services for iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t>6971070081104</t>
+          <t>195****94450</t>
         </is>
       </c>
       <c r="L651" t="n">
@@ -59259,17 +59259,17 @@
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>COOYEE可怡 iphone  18 Pro  Max波浪纹磁吸壳 白色</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>6971070081104</t>
         </is>
       </c>
       <c r="L654" t="n">
@@ -59335,12 +59335,12 @@
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K655" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L655" t="n">
@@ -59401,17 +59401,17 @@
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>AppleCare Services for iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="K656" t="inlineStr">
         <is>
-          <t>6927123816285</t>
+          <t>195****94450</t>
         </is>
       </c>
       <c r="L656" t="n">
@@ -59477,12 +59477,12 @@
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>6955482543900</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L657" t="n">
@@ -59543,17 +59543,17 @@
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 18 Pro Max</t>
+          <t>ZGA iPhone 18 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t>195****94450</t>
+          <t>6927123816285</t>
         </is>
       </c>
       <c r="L658" t="n">
@@ -59614,17 +59614,17 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>COOYEE可怡 iphone  18 Pro  Max波浪纹磁吸壳 白色</t>
+          <t>MAXCO美能格 MC55 60W 氮化镓快速充电器 白色</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>6971070081104</t>
+          <t>6955482543900</t>
         </is>
       </c>
       <c r="L659" t="n">
@@ -59969,17 +59969,17 @@
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 18 Pro Max</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 雅致黑</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
         <is>
-          <t>195****94450</t>
+          <t>6955482539514</t>
         </is>
       </c>
       <c r="L664" t="n">
@@ -60037,17 +60037,17 @@
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MP39 10000mAh 传奇二代磁吸快充移动电源</t>
+          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
         <is>
-          <t>6955482532911</t>
+          <t>6927123816537</t>
         </is>
       </c>
       <c r="L665" t="n">
@@ -60173,23 +60173,20 @@
       </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 18 Pro 冰川减震磁吸肤感保护壳 磨砂透明</t>
+          <t>MAXCO美能格 MP39 10000mAh 传奇二代磁吸快充移动电源</t>
         </is>
       </c>
       <c r="K667" t="inlineStr">
         <is>
-          <t>6980113280015</t>
+          <t>6955482532911</t>
         </is>
       </c>
       <c r="L667" t="n">
-        <v>1</v>
-      </c>
-      <c r="M667" t="n">
         <v>1</v>
       </c>
       <c r="N667" t="n">
@@ -60244,17 +60241,17 @@
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 雅致黑</t>
+          <t>AppleCare Services for iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
         <is>
-          <t>6955482539514</t>
+          <t>195****94450</t>
         </is>
       </c>
       <c r="L668" t="n">
@@ -60317,15 +60314,18 @@
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>ZGA iPhone 18 Pro / 18 Pro Max 裸感鹰眼镜头膜 透明</t>
+          <t>VOKAMO沃咔曼 iPhone 18 Pro 冰川减震磁吸肤感保护壳 磨砂透明</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
         <is>
-          <t>6927123816537</t>
+          <t>6980113280015</t>
         </is>
       </c>
       <c r="L669" t="n">
+        <v>1</v>
+      </c>
+      <c r="M669" t="n">
         <v>1</v>
       </c>
       <c r="N669" t="n">
@@ -60806,23 +60806,20 @@
       </c>
       <c r="I676" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>RICHIC锐壳iPhone 18 Pro Max 一体式柔雾晶透镜头膜 透明</t>
+          <t>AppleCare Services for iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="K676" t="inlineStr">
         <is>
-          <t>6978880671693</t>
+          <t>195****94450</t>
         </is>
       </c>
       <c r="L676" t="n">
-        <v>1</v>
-      </c>
-      <c r="M676" t="n">
         <v>1</v>
       </c>
       <c r="N676" t="n">
@@ -60877,17 +60874,17 @@
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>RICHIC锐壳iPhone 18 Pro Max 高清保护膜 透明</t>
+          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
         </is>
       </c>
       <c r="K677" t="inlineStr">
         <is>
-          <t>6978880671655</t>
+          <t>6941876245437</t>
         </is>
       </c>
       <c r="L677" t="n">
@@ -60948,20 +60945,23 @@
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 18 Pro Max</t>
+          <t>RICHIC锐壳iPhone 18 Pro Max 一体式柔雾晶透镜头膜 透明</t>
         </is>
       </c>
       <c r="K678" t="inlineStr">
         <is>
-          <t>195****94450</t>
+          <t>6978880671693</t>
         </is>
       </c>
       <c r="L678" t="n">
+        <v>1</v>
+      </c>
+      <c r="M678" t="n">
         <v>1</v>
       </c>
       <c r="N678" t="n">
@@ -61016,17 +61016,17 @@
       </c>
       <c r="I679" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 深灰色</t>
+          <t>RICHIC锐壳 iPhone 17 透明磨砂保护壳 透明</t>
         </is>
       </c>
       <c r="K679" t="inlineStr">
         <is>
-          <t>6928288527771</t>
+          <t>6978880670122</t>
         </is>
       </c>
       <c r="L679" t="n">
@@ -61163,12 +61163,12 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPhone 17 透明磨砂保护壳 透明</t>
+          <t>RICHIC锐壳iPhone 18 Pro Max 高清保护膜 透明</t>
         </is>
       </c>
       <c r="K681" t="inlineStr">
         <is>
-          <t>6978880670122</t>
+          <t>6978880671655</t>
         </is>
       </c>
       <c r="L681" t="n">
@@ -61229,17 +61229,17 @@
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
+          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 深灰色</t>
         </is>
       </c>
       <c r="K682" t="inlineStr">
         <is>
-          <t>6941876245437</t>
+          <t>6928288527771</t>
         </is>
       </c>
       <c r="L682" t="n">
@@ -61939,17 +61939,17 @@
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 氮化镓三口充电器 65W</t>
+          <t>RICHIC锐壳iPhone 18 Pro 透明磨砂磁吸保护壳 透明磨砂</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
         <is>
-          <t>6974623613029</t>
+          <t>6978880671563</t>
         </is>
       </c>
       <c r="L692" t="n">
@@ -62010,23 +62010,20 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 白色</t>
+          <t>AppleCare Services for iPhone 18 Pro</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
         <is>
-          <t>6928288555361</t>
+          <t>195****94443</t>
         </is>
       </c>
       <c r="L693" t="n">
-        <v>1</v>
-      </c>
-      <c r="M693" t="n">
         <v>1</v>
       </c>
       <c r="N693" t="n">
@@ -62081,20 +62078,23 @@
       </c>
       <c r="I694" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 18 Pro</t>
+          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 白色</t>
         </is>
       </c>
       <c r="K694" t="inlineStr">
         <is>
-          <t>195****94443</t>
+          <t>6928288555361</t>
         </is>
       </c>
       <c r="L694" t="n">
+        <v>1</v>
+      </c>
+      <c r="M694" t="n">
         <v>1</v>
       </c>
       <c r="N694" t="n">
@@ -62288,17 +62288,17 @@
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>RICHIC锐壳iPhone 18 Pro 透明磨砂磁吸保护壳 透明磨砂</t>
+          <t>RICHIC锐壳 氮化镓三口充电器 65W</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>6978880671563</t>
+          <t>6974623613029</t>
         </is>
       </c>
       <c r="L697" t="n">
@@ -63347,23 +63347,20 @@
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>Pocket</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>Osmo Pocket 4P 标准套装</t>
+          <t>大疆礼品袋（日常款-飞航）</t>
         </is>
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>6937224148321</t>
+          <t>FHQLSP0005</t>
         </is>
       </c>
       <c r="L712" t="n">
-        <v>1</v>
-      </c>
-      <c r="M712" t="n">
         <v>1</v>
       </c>
       <c r="N712" t="n">
@@ -63418,20 +63415,23 @@
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>遥控与控制</t>
+          <t>Pocket</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>DJI Mic Mini 2 （两发一收，含充电盒）</t>
+          <t>Osmo Pocket 4P 标准套装</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>6937224139749</t>
+          <t>6937224148321</t>
         </is>
       </c>
       <c r="L713" t="n">
+        <v>1</v>
+      </c>
+      <c r="M713" t="n">
         <v>1</v>
       </c>
       <c r="N713" t="n">
@@ -63486,17 +63486,17 @@
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>遥控与控制</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>大疆礼品袋（日常款-飞航）</t>
+          <t>DJI Mic Mini 2 （两发一收，含充电盒）</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>FHQLSP0005</t>
+          <t>6937224139749</t>
         </is>
       </c>
       <c r="L714" t="n">
@@ -63559,12 +63559,12 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>Osmo Action 6 标准套装</t>
+          <t>DJI Care 随心换 1年版（Osmo Action 6）中国版</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>6937224126060</t>
+          <t>6937224124783</t>
         </is>
       </c>
       <c r="L715" t="n">
@@ -63630,12 +63630,12 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo Action 6）中国版</t>
+          <t>Osmo Action 6 标准套装</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>6937224124783</t>
+          <t>6937224126060</t>
         </is>
       </c>
       <c r="L716" t="n">
@@ -63767,17 +63767,17 @@
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>Osmo 挂脖支架 Max</t>
+          <t>DJI Care 随心换 1年版（Osmo Action 6）中国版</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>6941565998507</t>
+          <t>6937224124783</t>
         </is>
       </c>
       <c r="L718" t="n">
@@ -63977,17 +63977,17 @@
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo Action 6）中国版</t>
+          <t>Osmo 挂脖支架 Max</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>6937224124783</t>
+          <t>6941565998507</t>
         </is>
       </c>
       <c r="L721" t="n">
@@ -64048,17 +64048,17 @@
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>Pocket</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>Osmo Pocket 4 全能套装</t>
+          <t>大疆礼品袋（日常款-飞航）</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>6937224133082</t>
+          <t>FHQLSP0005</t>
         </is>
       </c>
       <c r="L722" t="n">
@@ -64119,17 +64119,17 @@
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Pocket</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>大疆礼品袋（日常款-飞航）</t>
+          <t>Osmo Pocket 4 全能套装</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>FHQLSP0005</t>
+          <t>6937224133082</t>
         </is>
       </c>
       <c r="L723" t="n">
@@ -64190,17 +64190,17 @@
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>Osmo 360 标准套装</t>
+          <t>DJI 晴雨伞（中国区）</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>6937224110502</t>
+          <t>6941565984104</t>
         </is>
       </c>
       <c r="L724" t="n">
@@ -64261,17 +64261,17 @@
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>DJI 晴雨伞（中国区）</t>
+          <t>Osmo 360 标准套装</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>6941565984104</t>
+          <t>6937224110502</t>
         </is>
       </c>
       <c r="L725" t="n">
@@ -68118,17 +68118,17 @@
       </c>
       <c r="I780" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>MateBook 数字</t>
         </is>
       </c>
       <c r="J780" t="inlineStr">
         <is>
-          <t>礼品-配件-无线鼠标-CD23 SE-黑色-55036863</t>
+          <t>MateBook 14 MNTXM-24A(HarmonyOS 24GB+512GB) 柔光版 触屏 原野绿</t>
         </is>
       </c>
       <c r="K780" t="inlineStr">
         <is>
-          <t>A0890186</t>
+          <t>6942103196256</t>
         </is>
       </c>
       <c r="L780" t="n">
@@ -68189,17 +68189,17 @@
       </c>
       <c r="I781" t="inlineStr">
         <is>
-          <t>MateBook 数字</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J781" t="inlineStr">
         <is>
-          <t>MateBook 14 MNTXM-24A(HarmonyOS 24GB+512GB) 柔光版 触屏 原野绿</t>
+          <t>礼品-配件-无线鼠标-CD23 SE-黑色-55036863</t>
         </is>
       </c>
       <c r="K781" t="inlineStr">
         <is>
-          <t>6942103196256</t>
+          <t>A0890186</t>
         </is>
       </c>
       <c r="L781" t="n">
@@ -68686,17 +68686,17 @@
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>Mate 90</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>Mate 90 HLS-AL00(12GB+256GB) 曜石黑</t>
+          <t>礼品-定制-沙发嘿嘿摆件1</t>
         </is>
       </c>
       <c r="K788" t="inlineStr">
         <is>
-          <t>6942711326045</t>
+          <t>A0800812</t>
         </is>
       </c>
       <c r="L788" t="n">
@@ -68757,17 +68757,17 @@
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>Mate 90</t>
         </is>
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>礼品-定制-沙发嘿嘿摆件1</t>
+          <t>Mate 90 HLS-AL00(12GB+256GB) 曜石黑</t>
         </is>
       </c>
       <c r="K789" t="inlineStr">
         <is>
-          <t>A0800812</t>
+          <t>6942711326045</t>
         </is>
       </c>
       <c r="L789" t="n">
